--- a/events/Moscow_2016_ECH/Moscow_2016_ECH_Results.xlsx
+++ b/events/Moscow_2016_ECH/Moscow_2016_ECH_Results.xlsx
@@ -922,6 +922,11 @@
           <t>04:09.544</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1502,6 +1507,11 @@
           <t>04:00.280</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3182,6 +3192,11 @@
           <t>03:43.748</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3772,6 +3787,11 @@
           <t>53470</t>
         </is>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>53472</t>
@@ -3837,9 +3857,24 @@
           <t>01:21.592</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>63952</t>
+        </is>
+      </c>
       <c r="T52" t="inlineStr">
         <is>
           <t>51672</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>68980</t>
         </is>
       </c>
     </row>
@@ -4067,9 +4102,19 @@
           <t>47634</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>65034</t>
+        </is>
+      </c>
       <c r="T55" t="inlineStr">
         <is>
           <t>52099</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>54934</t>
         </is>
       </c>
     </row>
@@ -4137,6 +4182,11 @@
           <t>56668</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>71491</t>
+        </is>
+      </c>
       <c r="T56" t="inlineStr">
         <is>
           <t>62090</t>
@@ -5232,6 +5282,16 @@
           <t>03:39.772</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5507,6 +5567,11 @@
           <t>41591</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>53887</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5847,6 +5912,11 @@
           <t>03:14.416</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>52654</t>
+        </is>
+      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>36140</t>
@@ -6122,6 +6192,11 @@
           <t>42046</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6392,6 +6467,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7884,6 +7964,11 @@
           <t>01:48.012</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8784,6 +8869,11 @@
           <t>01:47.904</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8909,6 +8999,11 @@
           <t>01:48.796</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10074,6 +10169,11 @@
           <t>02:01.544</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10834,6 +10934,11 @@
           <t>36185</t>
         </is>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
       <c r="T156" t="inlineStr">
         <is>
           <t>36150</t>
@@ -10989,9 +11094,19 @@
           <t>47634</t>
         </is>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>65034</t>
+        </is>
+      </c>
       <c r="T158" t="inlineStr">
         <is>
           <t>52099</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>54934</t>
         </is>
       </c>
     </row>
@@ -11054,6 +11169,11 @@
           <t>03:38.968</t>
         </is>
       </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>71491</t>
+        </is>
+      </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>62090</t>
@@ -11134,6 +11254,11 @@
           <t>42049</t>
         </is>
       </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>41991</t>
@@ -11724,6 +11849,11 @@
           <t>01:39.708</t>
         </is>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12539,6 +12669,16 @@
           <t>01:39.473</t>
         </is>
       </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13779,6 +13919,11 @@
           <t>01:55.276</t>
         </is>
       </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>71491</t>
+        </is>
+      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>56668</t>
@@ -14331,6 +14476,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14526,6 +14676,11 @@
           <t>04:04.836</t>
         </is>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -16536,6 +16691,11 @@
           <t>03:51.032</t>
         </is>
       </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -16911,9 +17071,19 @@
           <t>47634</t>
         </is>
       </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>65034</t>
+        </is>
+      </c>
       <c r="T245" t="inlineStr">
         <is>
           <t>52099</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>54934</t>
         </is>
       </c>
     </row>
@@ -16976,6 +17146,11 @@
           <t>01:39.732</t>
         </is>
       </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>71491</t>
+        </is>
+      </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>62090</t>
@@ -17471,6 +17646,11 @@
           <t>41591</t>
         </is>
       </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>53887</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -18296,6 +18476,11 @@
           <t>03:12.360</t>
         </is>
       </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>52654</t>
+        </is>
+      </c>
       <c r="S265" t="inlineStr">
         <is>
           <t>36140</t>
@@ -18566,6 +18751,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -19276,6 +19466,11 @@
           <t>01:51.812</t>
         </is>
       </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -20881,6 +21076,11 @@
           <t>01:39.472</t>
         </is>
       </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -21401,6 +21601,11 @@
           <t>36185</t>
         </is>
       </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
       <c r="T313" t="inlineStr">
         <is>
           <t>36150</t>
@@ -21716,9 +21921,19 @@
           <t>47634</t>
         </is>
       </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>65034</t>
+        </is>
+      </c>
       <c r="T317" t="inlineStr">
         <is>
           <t>52099</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>54934</t>
         </is>
       </c>
     </row>
@@ -21851,6 +22066,11 @@
           <t>03:40.516</t>
         </is>
       </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>71491</t>
+        </is>
+      </c>
       <c r="S319" t="inlineStr">
         <is>
           <t>62090</t>
@@ -23311,6 +23531,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -24609,6 +24834,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -25068,6 +25298,11 @@
           <t>04:06.564</t>
         </is>
       </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -25532,6 +25767,11 @@
           <t>03:58.916</t>
         </is>
       </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -26609,6 +26849,11 @@
           <t>54250</t>
         </is>
       </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>47447</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -26964,6 +27209,16 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -27103,6 +27358,11 @@
           <t>01:34.360</t>
         </is>
       </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
       <c r="S396" t="inlineStr">
         <is>
           <t>42963</t>
@@ -27334,6 +27594,11 @@
           <t>42146</t>
         </is>
       </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
       <c r="U399" t="inlineStr">
         <is>
           <t>36186</t>
@@ -27488,6 +27753,11 @@
           <t>51727</t>
         </is>
       </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>63942</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -27555,6 +27825,11 @@
           <t>42117</t>
         </is>
       </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -28300,6 +28575,11 @@
           <t>53470</t>
         </is>
       </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
       <c r="U412" t="inlineStr">
         <is>
           <t>53472</t>
@@ -28367,9 +28647,24 @@
           <t>01:21.240</t>
         </is>
       </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>63952</t>
+        </is>
+      </c>
       <c r="T413" t="inlineStr">
         <is>
           <t>51672</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>68980</t>
         </is>
       </c>
     </row>
@@ -28762,6 +29057,16 @@
           <t>03:37.804</t>
         </is>
       </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -29621,6 +29926,11 @@
           <t>42046</t>
         </is>
       </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -29827,6 +30137,11 @@
           <t>03:17.528</t>
         </is>
       </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>52654</t>
+        </is>
+      </c>
       <c r="S433" t="inlineStr">
         <is>
           <t>36140</t>
@@ -30043,6 +30358,11 @@
           <t>36180</t>
         </is>
       </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
       <c r="T436" t="inlineStr">
         <is>
           <t>36183</t>
@@ -30284,6 +30604,11 @@
           <t>51708</t>
         </is>
       </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>51694</t>
+        </is>
+      </c>
       <c r="U439" t="inlineStr">
         <is>
           <t>52285</t>
@@ -30361,6 +30686,11 @@
           <t>47436</t>
         </is>
       </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
       <c r="U440" t="inlineStr">
         <is>
           <t>47429</t>
@@ -30655,6 +30985,11 @@
           <t>00:41.528</t>
         </is>
       </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>47447</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -30715,6 +31050,11 @@
           <t>00:42.156</t>
         </is>
       </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -31355,6 +31695,11 @@
           <t>00:41.540</t>
         </is>
       </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -32832,6 +33177,11 @@
           <t>00:36.028</t>
         </is>
       </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -33017,6 +33367,11 @@
           <t>00:37.840</t>
         </is>
       </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -34757,6 +35112,11 @@
           <t>00:53.680</t>
         </is>
       </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -34884,6 +35244,11 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -36319,6 +36684,11 @@
           <t>49674</t>
         </is>
       </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -37284,6 +37654,11 @@
           <t>44432</t>
         </is>
       </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>44433</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -37554,6 +37929,11 @@
           <t>00:43.020</t>
         </is>
       </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>47447</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -37999,6 +38379,11 @@
           <t>00:40.960</t>
         </is>
       </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -38834,6 +39219,11 @@
           <t>00:37.096</t>
         </is>
       </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -38959,6 +39349,11 @@
           <t>00:34.544</t>
         </is>
       </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -40114,6 +40509,11 @@
           <t>00:50.480</t>
         </is>
       </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -41054,6 +41454,11 @@
           <t>49674</t>
         </is>
       </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -41394,6 +41799,11 @@
           <t>44432</t>
         </is>
       </c>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>44433</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -43190,6 +43600,11 @@
           <t>01:51.784</t>
         </is>
       </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -43582,6 +43997,11 @@
           <t>01:50.548</t>
         </is>
       </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -43711,6 +44131,11 @@
           <t>01:52.076</t>
         </is>
       </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -44505,6 +44930,11 @@
           <t>01:42.392</t>
         </is>
       </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -44788,6 +45218,11 @@
           <t>36185</t>
         </is>
       </c>
+      <c r="S659" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
       <c r="T659" t="inlineStr">
         <is>
           <t>36150</t>
@@ -45111,6 +45546,11 @@
           <t>42049</t>
         </is>
       </c>
+      <c r="T663" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="U663" t="inlineStr">
         <is>
           <t>41991</t>
@@ -45568,6 +46008,11 @@
           <t>01:43.564</t>
         </is>
       </c>
+      <c r="S669" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -46052,6 +46497,16 @@
           <t>01:41.216</t>
         </is>
       </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -48127,6 +48582,11 @@
           <t>00:36.028</t>
         </is>
       </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -48519,6 +48979,11 @@
           <t>00:40.940</t>
         </is>
       </c>
+      <c r="R712" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -48715,6 +49180,11 @@
           <t>00:41.196</t>
         </is>
       </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -48911,6 +49381,11 @@
           <t>00:41.640</t>
         </is>
       </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>47447</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -50035,6 +50510,11 @@
           <t>00:35.204</t>
         </is>
       </c>
+      <c r="R735" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -50231,6 +50711,11 @@
           <t>00:47.616</t>
         </is>
       </c>
+      <c r="R738" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -50960,6 +51445,11 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="S749" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -52725,6 +53215,11 @@
           <t>22:23.450</t>
         </is>
       </c>
+      <c r="R774" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -53765,6 +54260,11 @@
           <t>22:15.350</t>
         </is>
       </c>
+      <c r="R790" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -54363,6 +54863,11 @@
           <t>24:46.620</t>
         </is>
       </c>
+      <c r="R799" t="inlineStr">
+        <is>
+          <t>47336</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -54425,6 +54930,11 @@
           <t>25:12.440</t>
         </is>
       </c>
+      <c r="R800" t="inlineStr">
+        <is>
+          <t>53887</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -54685,6 +55195,11 @@
           <t>20:12.420</t>
         </is>
       </c>
+      <c r="R804" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -56184,6 +56699,11 @@
           <t>00:49.768</t>
         </is>
       </c>
+      <c r="R827" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -57089,6 +57609,11 @@
           <t>00:38.652</t>
         </is>
       </c>
+      <c r="R841" t="inlineStr">
+        <is>
+          <t>56556</t>
+        </is>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -57543,6 +58068,11 @@
           <t>01:01.052</t>
         </is>
       </c>
+      <c r="R848" t="inlineStr">
+        <is>
+          <t>56560</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -59267,6 +59797,11 @@
           <t>00:53.736</t>
         </is>
       </c>
+      <c r="R874" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -59519,6 +60054,11 @@
           <t>00:49.512</t>
         </is>
       </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -60689,6 +61229,11 @@
           <t>00:53.628</t>
         </is>
       </c>
+      <c r="R896" t="inlineStr">
+        <is>
+          <t>80544</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -60818,6 +61363,11 @@
           <t>00:58.860</t>
         </is>
       </c>
+      <c r="R898" t="inlineStr">
+        <is>
+          <t>56560</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -61215,6 +61765,11 @@
           <t>01:02.980</t>
         </is>
       </c>
+      <c r="R904" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
@@ -61875,6 +62430,11 @@
           <t>00:49.736</t>
         </is>
       </c>
+      <c r="R914" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -61935,6 +62495,11 @@
       <c r="P915" t="inlineStr">
         <is>
           <t>00:40.028</t>
+        </is>
+      </c>
+      <c r="R915" t="inlineStr">
+        <is>
+          <t>56556</t>
         </is>
       </c>
     </row>
@@ -62485,7 +63050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D398"/>
+  <dimension ref="A1:D435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71244,6 +71809,820 @@
         </is>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>DRAHOKOUPIL</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>ANOSHKIN</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Ilia</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>SHTOKALOV</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Ilya</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>PERVUKHIN</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Alexey</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>KOROVASHKOV</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>PODOLSKAIA</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Viktor</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>MELANTEV</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>WALKER</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Miika</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>NYKAENEN</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Maryna</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>LITVINCHUK</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Mikhail</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>PAVLOV</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Aleksandr</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>SERGEEV</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Svetlana</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>CHERNIGOVSKAYA</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>44433</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Lubomir</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>BENO</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>47336</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Oleg</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>SHURINKIN</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Igor</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>KOROBEYNIKOV</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>47447</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Iuliana</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>TARAN</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Evgenii</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>LUKANTSOV</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Tamas</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>KISS</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Dzmitry</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>TRATSIAKOU</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>51694</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>PATAPENKA</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>52654</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Vladislav</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>LITOVKA</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Olesia</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>ROMASENKO</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>53887</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>JONES</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>54934</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Albert</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>PETERSSON</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>56556</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Leonid</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>KRYLOV</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Larisa</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>VOLIK</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>56560</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Pavel</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>GROMOV</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>63942</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Alena</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>NAZDROVA</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>63952</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Kiryl</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>NIKITSIN</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>65034</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Jhonny</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>BLIXT</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Mikita</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>BORYKAU</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>71491</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Edgar</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>TUTYAN</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>80544</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Andrei</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>TKACHUK</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Moscow_2016_ECH/Moscow_2016_ECH_Results.xlsx
+++ b/events/Moscow_2016_ECH/Moscow_2016_ECH_Results.xlsx
@@ -667,6 +667,11 @@
           <t>04:03.772</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4652,6 +4657,11 @@
           <t>01:23.188</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>46414</t>
@@ -7904,6 +7914,11 @@
           <t>01:47.748</t>
         </is>
       </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11639,6 +11654,11 @@
           <t>03:06.776</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>46364</t>
@@ -11914,6 +11934,11 @@
           <t>01:40.324</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="S169" t="inlineStr">
         <is>
           <t>42146</t>
@@ -16996,6 +17021,11 @@
           <t>01:21.308</t>
         </is>
       </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>46414</t>
@@ -21996,6 +22026,11 @@
           <t>03:01.424</t>
         </is>
       </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
       <c r="S318" t="inlineStr">
         <is>
           <t>46364</t>
@@ -22141,6 +22176,11 @@
           <t>01:41.648</t>
         </is>
       </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="S320" t="inlineStr">
         <is>
           <t>42146</t>
@@ -24901,6 +24941,11 @@
           <t>04:00.840</t>
         </is>
       </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -27517,6 +27562,11 @@
           <t>01:35.360</t>
         </is>
       </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="T398" t="inlineStr">
         <is>
           <t>42349</t>
@@ -34147,6 +34197,11 @@
           <t>00:35.396</t>
         </is>
       </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>36593</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -38834,6 +38889,11 @@
           <t>00:35.444</t>
         </is>
       </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>36593</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -43476,6 +43536,11 @@
           <t>01:49.576</t>
         </is>
       </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -46075,6 +46140,11 @@
           <t>01:43.936</t>
         </is>
       </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="S670" t="inlineStr">
         <is>
           <t>42146</t>
@@ -50247,6 +50317,11 @@
           <t>00:35.072</t>
         </is>
       </c>
+      <c r="R731" t="inlineStr">
+        <is>
+          <t>36593</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -53411,6 +53486,11 @@
           <t>22:36.470</t>
         </is>
       </c>
+      <c r="R777" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -55731,6 +55811,11 @@
           <t>20:56.280</t>
         </is>
       </c>
+      <c r="R812" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -56639,6 +56724,11 @@
           <t>00:48.568</t>
         </is>
       </c>
+      <c r="R826" t="inlineStr">
+        <is>
+          <t>54626</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -58470,6 +58560,11 @@
           <t>01:02.180</t>
         </is>
       </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>54626</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -59994,6 +60089,11 @@
           <t>00:48.828</t>
         </is>
       </c>
+      <c r="R877" t="inlineStr">
+        <is>
+          <t>54626</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -60703,6 +60803,11 @@
           <t>00:54.956</t>
         </is>
       </c>
+      <c r="R888" t="inlineStr">
+        <is>
+          <t>61471</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
@@ -62366,6 +62471,11 @@
       <c r="P913" t="inlineStr">
         <is>
           <t>00:49.344</t>
+        </is>
+      </c>
+      <c r="R913" t="inlineStr">
+        <is>
+          <t>54626</t>
         </is>
       </c>
     </row>
@@ -63050,7 +63160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D435"/>
+  <dimension ref="A1:D442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72623,6 +72733,160 @@
         </is>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>BEDEC</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Vitaliy</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>TSURKAN</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>JØRGENSEN</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>ANYSHINA</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>36593</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Aleksejs</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>RUNJANCEVS</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>54626</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Or</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>ATATO</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>61471</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Edina</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>MÜLLER</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
